--- a/artfynd/A 36309-2020 artfynd.xlsx
+++ b/artfynd/A 36309-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>126848714</v>
       </c>
       <c r="B3" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126848794</v>
       </c>
       <c r="B4" t="n">
-        <v>91866</v>
+        <v>91940</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126848866</v>
       </c>
       <c r="B6" t="n">
-        <v>91523</v>
+        <v>91597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
